--- a/scripts/Voice_Test_Matrix.xlsx
+++ b/scripts/Voice_Test_Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Voice Test Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Voice Test Matrix'!$A$1:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Voice Test Matrix'!$A$1:$J$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +499,11 @@
           <t>to_number</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -526,9 +532,10 @@
           <t>Brooke - Big Sister</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -557,9 +564,10 @@
           <t>Katie - Friendly Fixer</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -588,9 +596,10 @@
           <t>Jacqueline - Reassuring Agent</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -619,9 +628,10 @@
           <t>Autumn</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -650,9 +660,10 @@
           <t>Fahad</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -681,9 +692,10 @@
           <t>Expressive Narrator</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -712,9 +724,10 @@
           <t>Radiant Girl</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -743,9 +756,10 @@
           <t>Magnetic-voiced Male</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -774,9 +788,10 @@
           <t>Compelling Lady</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -805,9 +820,10 @@
           <t>Aussie Bloke</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -836,9 +852,10 @@
           <t>Captivating Female</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -867,9 +884,10 @@
           <t>albion</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -898,9 +916,10 @@
           <t>astra</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -929,9 +948,10 @@
           <t>alexis</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -960,9 +980,10 @@
           <t>Shubh</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -991,9 +1012,10 @@
           <t>Anushka</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1022,9 +1044,10 @@
           <t>Ashley</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1053,9 +1076,10 @@
           <t>Alex</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1084,9 +1108,10 @@
           <t>alloy</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1115,9 +1140,10 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1146,9 +1172,10 @@
           <t>ballad</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1177,9 +1204,10 @@
           <t>Abhi</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1208,9 +1236,10 @@
           <t>Ava</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1239,9 +1268,10 @@
           <t>Colton Rivers</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1270,9 +1300,10 @@
           <t>Dungeon Master</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1301,9 +1332,10 @@
           <t>Roger - Laid-Back, Casual, Resonant</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1332,9 +1364,10 @@
           <t>Sarah - Mature, Reassuring, Confident</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1363,9 +1396,10 @@
           <t>Laura - Enthusiast, Quirky Attitude</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1394,9 +1428,10 @@
           <t>Charlie - Deep, Confident, Energetic</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1425,9 +1460,10 @@
           <t>Pirate Captain</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1456,9 +1492,10 @@
           <t>British Butler</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1487,9 +1524,10 @@
           <t>Cartoon Villain</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1518,9 +1556,10 @@
           <t>Medieval Knight</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1549,9 +1588,10 @@
           <t>Nyomi</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1580,12 +1620,13 @@
           <t>Sarah</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I36"/>
+  <autoFilter ref="A1:J36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/scripts/Voice_Test_Matrix.xlsx
+++ b/scripts/Voice_Test_Matrix.xlsx
@@ -532,10 +532,24 @@
           <t>Brooke - Big Sister</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>+19894742667</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>LLM never responded, TTS only produced 5 chars (greeting only)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -564,9 +578,19 @@
           <t>Katie - Friendly Fixer</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>466</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>+16827328687</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
@@ -596,9 +620,19 @@
           <t>Jacqueline - Reassuring Agent</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>+15076506421</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="n"/>
     </row>
     <row r="5">
@@ -628,10 +662,24 @@
           <t>Autumn</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>467</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>+17405204895</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>TTS produced no audio (0 tts_usage entries)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -660,10 +708,24 @@
           <t>Fahad</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>471</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>+12183093029</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>TTS produced no audio (0 tts_usage entries)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -692,9 +754,19 @@
           <t>Expressive Narrator</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>472</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>+16562614918</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="n"/>
     </row>
     <row r="8">
@@ -724,9 +796,19 @@
           <t>Radiant Girl</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>+13186201704</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -756,9 +838,19 @@
           <t>Magnetic-voiced Male</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>+12763881949</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
@@ -788,9 +880,19 @@
           <t>Compelling Lady</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>+13186682645</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -820,9 +922,19 @@
           <t>Aussie Bloke</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>474</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>+13187133023</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="n"/>
     </row>
     <row r="12">
@@ -852,9 +964,19 @@
           <t>Captivating Female</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>+19894742667</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -884,9 +1006,19 @@
           <t>albion</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>476</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>+16827328687</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="n"/>
     </row>
     <row r="14">
@@ -916,9 +1048,19 @@
           <t>astra</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>478</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>+15076506421</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="n"/>
     </row>
     <row r="15">
@@ -948,9 +1090,19 @@
           <t>alexis</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>477</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>+17405204895</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="n"/>
     </row>
     <row r="16">
@@ -1044,9 +1196,19 @@
           <t>Ashley</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>+13186201704</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="n"/>
     </row>
     <row r="19">
@@ -1076,9 +1238,19 @@
           <t>Alex</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>+12763881949</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="n"/>
     </row>
     <row r="20">
@@ -1204,9 +1376,19 @@
           <t>Abhi</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>+16562614918</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="n"/>
     </row>
     <row r="24">
@@ -1236,9 +1418,19 @@
           <t>Ava</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>482</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>+13186201704</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="n"/>
     </row>
     <row r="25">
@@ -1268,9 +1460,19 @@
           <t>Colton Rivers</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>484</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>+12763881949</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="n"/>
     </row>
     <row r="26">
@@ -1300,9 +1502,19 @@
           <t>Dungeon Master</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>+13186682645</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -1332,9 +1544,19 @@
           <t>Roger - Laid-Back, Casual, Resonant</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>+13187133023</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="n"/>
     </row>
     <row r="28">
@@ -1364,9 +1586,19 @@
           <t>Sarah - Mature, Reassuring, Confident</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>+16562614918</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="n"/>
     </row>
     <row r="29">
@@ -1396,9 +1628,19 @@
           <t>Laura - Enthusiast, Quirky Attitude</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>+13186201704</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="n"/>
     </row>
     <row r="30">
@@ -1428,9 +1670,19 @@
           <t>Charlie - Deep, Confident, Energetic</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>489</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>+12763881949</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="n"/>
     </row>
     <row r="31">
@@ -1460,9 +1712,19 @@
           <t>Pirate Captain</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>488</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>+13186682645</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="n"/>
     </row>
     <row r="32">
@@ -1492,9 +1754,19 @@
           <t>British Butler</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>491</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>+13187133023</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="n"/>
     </row>
     <row r="33">
@@ -1524,9 +1796,19 @@
           <t>Cartoon Villain</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>495</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>+16562614918</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="n"/>
     </row>
     <row r="34">
@@ -1556,9 +1838,19 @@
           <t>Medieval Knight</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>492</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>+13186201704</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="n"/>
     </row>
     <row r="35">
@@ -1588,9 +1880,19 @@
           <t>Nyomi</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>+12763881949</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="n"/>
     </row>
     <row r="36">
@@ -1620,9 +1922,19 @@
           <t>Sarah</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>+13186682645</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="n"/>
     </row>
   </sheetData>
